--- a/data/intermediate/Base_finalA_N_aleatoria_hombres_cohorte_actual_semilla_20260923.xlsx
+++ b/data/intermediate/Base_finalA_N_aleatoria_hombres_cohorte_actual_semilla_20260923.xlsx
@@ -476,7 +476,7 @@
         <v>49</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -499,7 +499,7 @@
         <v>50</v>
       </c>
       <c r="B3">
-        <v>439</v>
+        <v>386</v>
       </c>
       <c r="C3">
         <v>386</v>
@@ -561,7 +561,7 @@
         <v>51</v>
       </c>
       <c r="B4">
-        <v>422</v>
+        <v>376</v>
       </c>
       <c r="C4">
         <v>376</v>
@@ -623,7 +623,7 @@
         <v>52</v>
       </c>
       <c r="B5">
-        <v>381</v>
+        <v>341</v>
       </c>
       <c r="C5">
         <v>341</v>
@@ -682,7 +682,7 @@
         <v>53</v>
       </c>
       <c r="B6">
-        <v>398</v>
+        <v>353</v>
       </c>
       <c r="C6">
         <v>353</v>
@@ -747,7 +747,7 @@
         <v>54</v>
       </c>
       <c r="B7">
-        <v>423</v>
+        <v>358</v>
       </c>
       <c r="C7">
         <v>358</v>
@@ -818,7 +818,7 @@
         <v>55</v>
       </c>
       <c r="B8">
-        <v>387</v>
+        <v>339</v>
       </c>
       <c r="C8">
         <v>339</v>
@@ -886,7 +886,7 @@
         <v>56</v>
       </c>
       <c r="B9">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="C9">
         <v>315</v>
@@ -948,7 +948,7 @@
         <v>57</v>
       </c>
       <c r="B10">
-        <v>392</v>
+        <v>360</v>
       </c>
       <c r="C10">
         <v>360</v>
@@ -1019,7 +1019,7 @@
         <v>58</v>
       </c>
       <c r="B11">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="C11">
         <v>297</v>
@@ -1078,7 +1078,7 @@
         <v>59</v>
       </c>
       <c r="B12">
-        <v>392</v>
+        <v>356</v>
       </c>
       <c r="C12">
         <v>356</v>
@@ -1137,7 +1137,7 @@
         <v>60</v>
       </c>
       <c r="B13">
-        <v>394</v>
+        <v>354</v>
       </c>
       <c r="C13">
         <v>354</v>
@@ -1202,7 +1202,7 @@
         <v>61</v>
       </c>
       <c r="B14">
-        <v>375</v>
+        <v>342</v>
       </c>
       <c r="C14">
         <v>342</v>
@@ -1267,7 +1267,7 @@
         <v>62</v>
       </c>
       <c r="B15">
-        <v>348</v>
+        <v>312</v>
       </c>
       <c r="C15">
         <v>312</v>
@@ -1335,7 +1335,7 @@
         <v>63</v>
       </c>
       <c r="B16">
-        <v>338</v>
+        <v>302</v>
       </c>
       <c r="C16">
         <v>302</v>
@@ -1388,7 +1388,7 @@
         <v>64</v>
       </c>
       <c r="B17">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="C17">
         <v>309</v>
@@ -1456,7 +1456,7 @@
         <v>65</v>
       </c>
       <c r="B18">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="C18">
         <v>372</v>
@@ -1521,7 +1521,7 @@
         <v>66</v>
       </c>
       <c r="B19">
-        <v>378</v>
+        <v>349</v>
       </c>
       <c r="C19">
         <v>349</v>
@@ -1586,7 +1586,7 @@
         <v>67</v>
       </c>
       <c r="B20">
-        <v>355</v>
+        <v>325</v>
       </c>
       <c r="C20">
         <v>325</v>
@@ -1648,7 +1648,7 @@
         <v>68</v>
       </c>
       <c r="B21">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="C21">
         <v>328</v>
@@ -1716,7 +1716,7 @@
         <v>69</v>
       </c>
       <c r="B22">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="C22">
         <v>313</v>
@@ -1784,7 +1784,7 @@
         <v>70</v>
       </c>
       <c r="B23">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="C23">
         <v>314</v>
@@ -1846,7 +1846,7 @@
         <v>71</v>
       </c>
       <c r="B24">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="C24">
         <v>302</v>
@@ -1911,7 +1911,7 @@
         <v>72</v>
       </c>
       <c r="B25">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="C25">
         <v>259</v>
@@ -1973,7 +1973,7 @@
         <v>73</v>
       </c>
       <c r="B26">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="C26">
         <v>218</v>
@@ -2029,7 +2029,7 @@
         <v>74</v>
       </c>
       <c r="B27">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="C27">
         <v>244</v>
@@ -2085,7 +2085,7 @@
         <v>75</v>
       </c>
       <c r="B28">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="C28">
         <v>143</v>
@@ -2167,7 +2167,7 @@
     </row>
     <row r="30">
       <c r="B30">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C30">
         <v>9</v>
